--- a/data/data_cleaning_check_versions .xlsx
+++ b/data/data_cleaning_check_versions .xlsx
@@ -2,18 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr showObjects="none" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Zoha Shahabuddin\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Time Periods\Spring 2025\Conjoint_Survey_25\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2776D84F-E1B5-4993-A388-AAF123546E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52B18DC-CCBC-4E88-93AC-ED7AD870A289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AB398583-1D6C-44A7-B644-39DAA0507635}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{AB398583-1D6C-44A7-B644-39DAA0507635}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="Prolific Round 2-4" sheetId="2" r:id="rId2"/>
+    <sheet name="Prolific Round 1" sheetId="3" r:id="rId3"/>
+    <sheet name="Dynata Round 1 " sheetId="4" r:id="rId4"/>
+    <sheet name="dynata_prolific_joint" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="60">
   <si>
     <t>prolific_testing_0_complete_response</t>
   </si>
@@ -102,13 +106,228 @@
   </si>
   <si>
     <t>Prolific Round 4</t>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">630 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">812 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>560</t>
+    </r>
+  </si>
+  <si>
+    <t>Round 2</t>
+  </si>
+  <si>
+    <t>Round 3</t>
+  </si>
+  <si>
+    <t>Round 4</t>
+  </si>
+  <si>
+    <t>rounds</t>
+  </si>
+  <si>
+    <t># removing testing entries</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">623 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">801 </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF3B3B3B"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>558</t>
+    </r>
+  </si>
+  <si>
+    <t># Drop people who got screened out</t>
+  </si>
+  <si>
+    <t># Survey Reponses</t>
+  </si>
+  <si>
+    <t>727 844 791</t>
+  </si>
+  <si>
+    <t># Removing duplicate Prolific IDs</t>
+  </si>
+  <si>
+    <t>727 844 790</t>
+  </si>
+  <si>
+    <t># Drop those who missed attention checks</t>
+  </si>
+  <si>
+    <t># Drop people whose next vehicle is NUll</t>
+  </si>
+  <si>
+    <t>727 843 790</t>
+  </si>
+  <si>
+    <t># Drop bad respondents</t>
+  </si>
+  <si>
+    <t>623 722 662</t>
+  </si>
+  <si>
+    <t># Drop anyone who didn't complete all choice questions</t>
+  </si>
+  <si>
+    <t># Drop anyone who got the demo question wrong:</t>
+  </si>
+  <si>
+    <t>527 579 500</t>
+  </si>
+  <si>
+    <t># Drop anyone who answered the same question for all choice questions</t>
+  </si>
+  <si>
+    <t>514 568 488</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>0_complete_response</t>
+  </si>
+  <si>
+    <t>1a_dce_cleaning_vehicle</t>
+  </si>
+  <si>
+    <t>Drop respondents who went too fast &lt; 30 sec</t>
+  </si>
+  <si>
+    <t># Drop anyone who answered the same question for all choice questions except no-choice</t>
+  </si>
+  <si>
+    <t>597 706 645</t>
+  </si>
+  <si>
+    <t># Drop anyone who finished the choice question section in under 30 seconds</t>
+  </si>
+  <si>
+    <t>1b_dce_cleaning_battery</t>
+  </si>
+  <si>
+    <t>PROLIFIC DATA (Rounds  2 -4)</t>
+  </si>
+  <si>
+    <t>PROLIFIC DATA (Round 1)</t>
+  </si>
+  <si>
+    <t>DYNATA DATA (Round 1)</t>
+  </si>
+  <si>
+    <t>Folder - dynata_testing</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Folder - prolific_testing</t>
+  </si>
+  <si>
+    <t>Folder - prolific_testing -round1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,13 +341,74 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3B3B3B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF3B3B3B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FF3B3B3B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -158,11 +438,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -174,6 +451,46 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -513,7 +830,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.42578125" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
     <col min="6" max="6" width="36.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.28515625" customWidth="1"/>
     <col min="11" max="11" width="41.7109375" customWidth="1"/>
@@ -521,437 +838,437 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="F1" s="1" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="F1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="K1" s="1" t="s">
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="K1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+    </row>
+    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>2360</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>1570</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="1">
         <v>790</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>1570</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <f>H5+M5</f>
         <v>1570</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="1">
         <v>1082</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="1">
         <v>488</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" spans="1:13" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="6" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>2238</v>
       </c>
-      <c r="D7" s="3">
-        <f t="shared" ref="D6:D7" si="0">H7+M7</f>
+      <c r="D7" s="2">
+        <f t="shared" ref="D7" si="0">H7+M7</f>
         <v>2238</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="1">
         <v>1486</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="1">
         <v>752</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:13" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="s">
+    <row r="8" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:13" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>403</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L11" s="4" t="s">
+      <c r="K11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="5" t="s">
+    <row r="12" spans="1:13" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="2">
         <v>1570</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="5" t="s">
+      <c r="F12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L12" s="5" t="s">
+      <c r="K12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:13" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="4" t="s">
+    <row r="13" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:13" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>489</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L14" s="4" t="s">
+      <c r="K14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="5" t="s">
+    <row r="15" spans="1:13" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="2">
         <v>2238</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="F15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L15" s="5" t="s">
+      <c r="K15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:12" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="4" t="s">
+    <row r="16" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="1:12" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="2">
         <v>281</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="F17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L17" s="4" t="s">
+      <c r="K17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="1:12" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>332</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="F18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L18" s="4" t="s">
+      <c r="K18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="5" t="s">
+    <row r="19" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:12" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="2">
         <v>2254</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="2">
         <f>C11+C12+C17</f>
         <v>2254</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G20" s="5" t="s">
+      <c r="F20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="2">
         <f>H11+H12+H17</f>
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L20" s="5" t="s">
+      <c r="K20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L20" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="5" t="s">
+    <row r="21" spans="1:12" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="2">
         <v>3059</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="2">
         <f>C14+C15+C18</f>
         <v>3059</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G21" s="5" t="s">
+      <c r="F21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="2">
         <f>H14+H15+H18</f>
         <v>0</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L21" s="5" t="s">
+      <c r="K21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="5" t="s">
+    <row r="22" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:12" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="2">
         <v>419</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="F23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L23" s="5" t="s">
+      <c r="K23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L23" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="5" t="s">
+    <row r="24" spans="1:12" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="2">
         <v>2851</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="5" t="s">
+      <c r="F24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L24" s="5" t="s">
+      <c r="K24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L24" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:12" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="5" t="s">
+    <row r="25" spans="1:12" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="2">
         <v>3270</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="5" t="s">
+      <c r="F25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L25" s="5" t="s">
+      <c r="K25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:C1"/>
@@ -960,4 +1277,1280 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14D4FCB5-75CE-4E5A-B2B6-B982B70BC3C7}">
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="102.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B1" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="12"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="8">
+        <v>5002</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1630</v>
+      </c>
+      <c r="F4" s="8">
+        <v>1812</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="8">
+        <v>4982</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1623</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1801</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="10">
+        <v>2362</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="8">
+        <v>727</v>
+      </c>
+      <c r="F8" s="8">
+        <v>844</v>
+      </c>
+      <c r="G8" s="8">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="10">
+        <v>2361</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="8">
+        <v>727</v>
+      </c>
+      <c r="F10" s="8">
+        <v>844</v>
+      </c>
+      <c r="G10" s="8">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="10">
+        <v>2361</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="8">
+        <v>727</v>
+      </c>
+      <c r="F12" s="8">
+        <v>844</v>
+      </c>
+      <c r="G12" s="8">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="B14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="10">
+        <v>2360</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="8">
+        <v>727</v>
+      </c>
+      <c r="F14" s="8">
+        <v>843</v>
+      </c>
+      <c r="G14" s="8">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="10">
+        <v>2007</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="8">
+        <v>623</v>
+      </c>
+      <c r="F16" s="8">
+        <v>722</v>
+      </c>
+      <c r="G16" s="8">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2007</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="8">
+        <v>623</v>
+      </c>
+      <c r="F18" s="8">
+        <v>722</v>
+      </c>
+      <c r="G18" s="8">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="10">
+        <v>1606</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="8">
+        <v>527</v>
+      </c>
+      <c r="F20" s="8">
+        <v>579</v>
+      </c>
+      <c r="G20" s="8">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="13"/>
+      <c r="B22" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="10">
+        <v>1606</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="8">
+        <v>527</v>
+      </c>
+      <c r="F22" s="8">
+        <v>579</v>
+      </c>
+      <c r="G22" s="8">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="13"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="13"/>
+      <c r="B24" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="10">
+        <v>1570</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="8">
+        <v>514</v>
+      </c>
+      <c r="F24" s="8">
+        <v>568</v>
+      </c>
+      <c r="G24" s="8">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="10">
+        <v>2007</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="8">
+        <v>623</v>
+      </c>
+      <c r="F26" s="8">
+        <v>722</v>
+      </c>
+      <c r="G26" s="8">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="13"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="13"/>
+      <c r="B28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="10">
+        <v>2007</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="8">
+        <v>623</v>
+      </c>
+      <c r="F28" s="8">
+        <v>722</v>
+      </c>
+      <c r="G28" s="8">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="13"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="13"/>
+      <c r="B30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="10">
+        <v>2007</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="8">
+        <v>623</v>
+      </c>
+      <c r="F30" s="8">
+        <v>722</v>
+      </c>
+      <c r="G30" s="8">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="13"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="13"/>
+      <c r="B32" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="10">
+        <v>1948</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="8">
+        <v>597</v>
+      </c>
+      <c r="F32" s="8">
+        <v>706</v>
+      </c>
+      <c r="G32" s="8">
+        <v>645</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A4:A14"/>
+    <mergeCell ref="A16:A24"/>
+    <mergeCell ref="A26:A32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F6C7C17-2E09-4038-A1F7-34F08BFFEE20}">
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="102.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B1" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="12"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1510</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1502</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="10">
+        <v>712</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="10">
+        <v>708</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="10">
+        <v>708</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="B14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="10">
+        <v>708</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="10">
+        <v>602</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="10">
+        <v>602</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="10">
+        <v>517</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="13"/>
+      <c r="B22" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="10">
+        <v>517</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="13"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="13"/>
+      <c r="B24" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="10">
+        <v>502</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="10">
+        <v>602</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="13"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="13"/>
+      <c r="B28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="10">
+        <v>602</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="13"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="13"/>
+      <c r="B30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="10">
+        <v>602</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="13"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="13"/>
+      <c r="B32" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="10">
+        <v>576</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A4:A14"/>
+    <mergeCell ref="A16:A24"/>
+    <mergeCell ref="A26:A32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC31648E-A704-4418-85E0-A6EAAFF752CE}">
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="102.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B1" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="12"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="16">
+        <v>1512</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="16">
+        <v>1487</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="8"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="17">
+        <v>594</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="13"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="8"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="8"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="17">
+        <v>594</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="13"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="B14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="17">
+        <v>593</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="17">
+        <v>588</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13"/>
+      <c r="B20" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="17">
+        <v>387</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="13"/>
+      <c r="B22" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="17">
+        <v>352</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="13"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="8"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="13"/>
+      <c r="B24" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="17">
+        <v>281</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="11"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="13"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="13"/>
+      <c r="B28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="19">
+        <v>589</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="13"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="13"/>
+      <c r="B30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="19">
+        <v>575</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="13"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="8"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="13"/>
+      <c r="B32" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="19">
+        <v>382</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A4:A14"/>
+    <mergeCell ref="A16:A24"/>
+    <mergeCell ref="A26:A32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE21F8E2-849E-4973-A923-8AB659A41A31}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="42.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:3" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2906</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2991</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>